--- a/data/2026-09/reporte_2026-09-11.xlsx
+++ b/data/2026-09/reporte_2026-09-11.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚨 Flujo Completo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 Adjudicaciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📰 BORA Licitaciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ Riesgo Licitatorio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,40 +416,4642 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>fecha</t>
+          <t>organismo_contratante</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>detalle</t>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>en_comprar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>procesos_comprar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unidad_comprar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>nro_proceso_comprar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cobro_en_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>beneficiario_tgn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>monto_cobrado_tgn</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metodo_cruce_tgn</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sin datos — todos los servicios externos fallaron</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 11:27</t>
+          <t>BIBLIOTECA DEL CONGRESO DE LA NACIÓN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BORA / Comprar / TGN no respondieron. Reintentar mañana.</t>
+          <t>Licitación Pública 002/26</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417321/20260911</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BANCO PATAGONIA S.A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitación Pública (Modo IV) 06/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417322/20260911</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL OESTE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417323/20260911</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30-70746458-1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>$15.660.000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE SEMILLAS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 2/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417324/20260911</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MAC S.R.L.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30-64640840-3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA HIDROVÍA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 41/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417325/20260911</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES GZCRON S.A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30-71595775-9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>$247.265.000,00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>🟡 Monto Límite ($247,265,000 justo bajo el tope de 5,000 módulos)</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Licitación Pública 482/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417326/20260911</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TUX SA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30-71434715-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>$39.457.800,00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>texto_muestra</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BIBLIOTECA DEL CONGRESO DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 002/26</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2417321</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417321/20260911</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>BANCO PATAGONIA S.A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/eEMyU01ZNGJGT2xSbkVWUVVZR3c4dz09
+BIBLIOTECA DEL CONGRESO DE LA NACIÓN
+Licitación Pública 002/26
+EXPEDIENTE N° 222/26 OBJETO: Contratación del servicio de pago de remuneraciones al personal de
+la Biblioteca del Congreso de la Nación. PREADJUDICATARIO: “</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública (Modo IV) 06/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2417322</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417322/20260911</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/c2xzQTFvME05TmxSbkVWUVVZR3c4dz09
+EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.
+Licitación Pública (Modo IV) 06/2026
+Procedimiento: MESA DE COMPRAS: Licitación Pública (Modo IV) Nº 06/2026. SOLPED Nº 11.000.038
+“Servicio de mantenimiento integral de predio</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL OESTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2417323</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417323/20260911</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>30-70746458-1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>$15.660.000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/cDYraDdDNmxmVzFSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL OESTE
+Licitación Pública 04/2025
+Expediente  N°:  EX-2025-00811645-  -ARCA-SGCFDVADMO#SDGOPIM  Objeto  de  la  contratación:
+Servicio de mantenimiento corre</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE SEMILLAS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 2/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2417324</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417324/20260911</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MAC S.R.L.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30-64640840-3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/RElGQnBtY05EVmhSbkVWUVVZR3c4dz09
+INSTITUTO NACIONAL DE SEMILLAS
+Licitación Pública 2/2026
+UOC: 50 - Departamento de Compras y Contrataciones Ejercicio: 2026 Clase: Única Nacional Modalidad:
+Sin modalidad Expediente N°: EX-2026-38975612- -APN-DA#INASE O</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA HIDROVÍA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 41/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2417325</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417325/20260911</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>OBRAS CIVILES GZCRON S.A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>30-71595775-9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>$247.265.000,00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/SmNJUDVYaWpKdEpSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA HIDROVÍA
+Licitación Pública 41/2026
+Ejercicio:  2026  Expediente  Nº:  EX-2026-01971887-  -ARCA-SECFDVAFHI#SDGOAI  Objeto  de  la
+contratación: “AD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Licitación Pública 482/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2417326</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417326/20260911</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TUX SA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>30-71434715-9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>$39.457.800,00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/bDBCc1JlaXphaU5SbkVWUVVZR3c4dz09
+EJÉRCITO ARGENTINO
+Licitación Pública 482/2026
+UOC: 84/40 - Comando Brigada Mecanizada X Ejercicio: 2026 Clase: Única Nacional Modalidad: Orden
+de compra abierta Expediente N°: EX-2026-66020573- -APN-CBMX#EA Objeto: ADQ</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>es_adjudicacion</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INVESTIGACIÓN Y DESARROLLO PESQUERO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0004/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - COMBUSTIBLES, LUBRICANTES Y ACEITES</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2417329</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417329/20260911</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN NACIONAL DE VIALIDAD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0029/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2417330</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417330/20260911</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN NACIONAL DE VIALIDAD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0033/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2417331</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417331/20260911</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0396/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2417332</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417332/20260911</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0633/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2417333</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417333/20260911</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Licitación Pública 584/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2417334</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417334/20260911</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Licitación Pública 593/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2417335</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417335/20260911</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Contratación Directa CD 15/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2417336</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417336/20260911</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional 47-2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2417337</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417337/20260911</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTA COMPLEJIDAD CUENCA ALTA DR. NÉSTOR CARLOS KIRCHNER (S.A.M.I.C)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Licitación Pública 067/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2417338</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417338/20260911</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0151/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - ELECTRICIDAD Y FERRETERIA ELECTRICA.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2417339</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417339/20260911</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Licitación Pública 353/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - ELECTRICIDAD Y FERRETERIA ELECTRICA.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2417340</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417340/20260911</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SINDICATURA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0001/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. PROC. AUTOMATICO DE DATOS, SOFT., SUM.Y EQ. APOYO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2417341</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417341/20260911</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Licitación Pública 33/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. PROC. AUTOMATICO DE DATOS, SOFT., SUM.Y EQ. APOYO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2417342</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417342/20260911</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0117/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. DE PLOMERIA, CALEFACCION Y SANITARIOS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2417343</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417343/20260911</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SALUD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0065/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2417344</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417344/20260911</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE PEDIATRÍA S.A.M.I.C. “PROF. DR. JUAN P. GARRAHAN”</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Licitación Pública 65/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2417345</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417345/20260911</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTA COMPLEJIDAD CUENCA ALTA DR. NÉSTOR CARLOS KIRCHNER (S.A.M.I.C)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Licitación Pública 064/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2417346</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417346/20260911</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR. RENÉ FAVALORO – (S.A.M.I.C.)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Licitación Pública 10/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2417347</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417347/20260911</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR. RENÉ FAVALORO – (S.A.M.I.C.)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Licitación Pública 11/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2417348</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417348/20260911</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Licitación Privada 95-2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2417349</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417349/20260911</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Licitación Privada 97-2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2417350</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417350/20260911</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Concurso Privado BCYL0170/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2417351</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417351/20260911</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Concurso Privado BCYL0171/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2417352</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417352/20260911</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Concurso Privado BCYL0172/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2417353</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417353/20260911</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Concurso Privado BCYL0173/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2417354</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417354/20260911</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Concurso Privado BCYL0174/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2417355</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417355/20260911</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Concurso Privado BCYL0176/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2417356</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417356/20260911</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PODER JUDICIAL DE LA NACIÓN - CONSEJO DE LA MAGISTRATURA - ADMINISTRACIÓN GENERAL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Licitación Pública 576/26</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - MAQUINAS Y SUMINISTROS PARA OFICINA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2417357</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417357/20260911</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Licitación Pública 349/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - MATERIALES DE FERRETERIA Y ABRASIVOS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2417358</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417358/20260911</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0419/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PINCELES, PINTURAS, SELLADORES Y ADHESIVOS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2417359</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417359/20260911</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE INVESTIGACIÓN Y DESARROLLO PESQUERO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Concurso Público 0006/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2417360</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417360/20260911</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0150/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2417361</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417361/20260911</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0624/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2417362</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417362/20260911</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0625/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2417363</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417363/20260911</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0634/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2417364</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417364/20260911</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE LA YERBA MATE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Licitación Pública 03/26</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - VEHICULOS EF. SUELO, AUTOMOT., ACOPLADOS,CICLISMO</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2417365</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417365/20260911</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LA PLATA - SECRETARÍA DE PLANEAMIENTO, OBRAS Y SERVICIOS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Licitación Pública 09/26</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2417366</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417366/20260911</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Licitación Pública 22/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SERVICIOS - LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2417367</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417367/20260911</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA NOROESTE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Licitación Pública 25/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SERVICIOS - LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2417368</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417368/20260911</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA NORESTE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Licitación Pública 65/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SERVICIOS - LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2417369</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417369/20260911</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>COMISIÓN NACIONAL DE VALORES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0005/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2417370</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417370/20260911</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE CINE Y ARTES AUDIOVISUALES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0006/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2417371</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417371/20260911</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN NACIONAL DE MIGRACIONES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0013/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2417372</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417372/20260911</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BUENOS AIRES - DIRECCIÓN GENERAL DE PLANIFICACIÓN Y GESTIÓN DE CONTRATACIONES</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Licitación Pública 009/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2417373</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417373/20260911</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0406/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2417374</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417374/20260911</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0455/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2417375</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417375/20260911</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0623/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2417376</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417376/20260911</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE CÓRDOBA - SECRETARÍA DE PLANEAMIENTO FÍSICO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Licitación Pública 194/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2417377</t>
+        </is>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417377/20260911</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO FISCAL - PROCURACIÓN GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Licitación Pública 26/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2417378</t>
+        </is>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417378/20260911</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA NOROESTE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Licitación Pública 26/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2417379</t>
+        </is>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417379/20260911</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Licitación Pública 26/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2417380</t>
+        </is>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417380/20260911</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE CINE Y ARTES AUDIOVISUALES</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Licitación Pública 4/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2417381</t>
+        </is>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417381/20260911</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PODER JUDICIAL DE LA NACIÓN - CONSEJO DE LA MAGISTRATURA - ADMINISTRACIÓN GENERAL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Licitación Pública 574/26</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2417382</t>
+        </is>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417382/20260911</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PODER JUDICIAL DE LA NACIÓN - CONSEJO DE LA MAGISTRATURA - ADMINISTRACIÓN GENERAL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Licitación Pública 575/26</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2417383</t>
+        </is>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417383/20260911</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA NORESTE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Licitación Pública 63/26</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2417384</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417384/20260911</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LA PLATA - SECRETARÍA DE PLANEAMIENTO, OBRAS Y SERVICIOS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Licitación Pública 8/26</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2417385</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417385/20260911</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Concurso Privado BCYL0175/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2417386</t>
+        </is>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417386/20260911</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BANCO DE LA NACIÓN ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Licitación Pública INM 6111</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2417387</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417387/20260911</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional 42-2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2417388</t>
+        </is>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417388/20260911</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional 46-2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2417389</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417389/20260911</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN DE OBRA SOCIAL DEL SERVICIO PENITENCIARIO FEDERAL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Selección por Concurso SPC-4-2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2417390</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417390/20260911</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AGENCIA DE ADMINISTRACIÓN DE BIENES DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Concurso Público 4/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - CONCESIONES</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2417391</t>
+        </is>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417391/20260911</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Subasta Pública 0010/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - INMUEBLES</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2417392</t>
+        </is>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417392/20260911</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AGENCIA DE ADMINISTRACIÓN DE BIENES DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Subasta Pública 392-0086-SPU26</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - INMUEBLES</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2417393</t>
+        </is>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417393/20260911</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AGENCIA DE ADMINISTRACIÓN DE BIENES DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Subasta Pública 392-0095-SPU26</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - INMUEBLES</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2417317</t>
+        </is>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417317/20260911</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL SANTA FE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Licitación Pública 02/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LOCACIONES - INMUEBLES (LOC)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2417318</t>
+        </is>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417318/20260911</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO FISCAL - PROCURACIÓN GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Licitación Pública 27/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LOCACIONES - INMUEBLES (LOC)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2417319</t>
+        </is>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417319/20260911</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA NORESTE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Licitación Pública 59/26</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LOCACIONES - INMUEBLES (LOC)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2417320</t>
+        </is>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417320/20260911</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0377/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DICTAMEN DE EVALUACION - DICTAMEN DE EVALUACION</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2417327</t>
+        </is>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417327/20260911</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA NORESTE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Licitación Pública 58/26</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DICTAMEN DE EVALUACION - DICTAMEN DE EVALUACION</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2417328</t>
+        </is>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417328/20260911</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA HIDROVÍA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 41/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30-71595775-9</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>$247.265.000,00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🟡 Monto Límite ($247,265,000 justo bajo el tope de 5,000 módulos)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417325/20260911</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BIBLIOTECA DEL CONGRESO DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 002/26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417321/20260911</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EMPRESA ARGENTINA DE NAVEGACIÓN AÉREA S.E.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Licitación Pública (Modo IV) 06/2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417322/20260911</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL OESTE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>30-70746458-1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>$15.660.000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417323/20260911</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE SEMILLAS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 2/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30-64640840-3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417324/20260911</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Licitación Pública 482/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>30-71434715-9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>$39.457.800,00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2417326/20260911</t>
         </is>
       </c>
     </row>
